--- a/output/tables/mi_full_models_pooled.xlsx
+++ b/output/tables/mi_full_models_pooled.xlsx
@@ -427,31 +427,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.766606553076068E+16</v>
+        <v>8.649868857954642E+21</v>
       </c>
       <c r="D2">
-        <v>37.28804123180329</v>
+        <v>42.33925090122496</v>
       </c>
       <c r="E2">
-        <v>1.015311658519328</v>
+        <v>1.193026093697664</v>
       </c>
       <c r="F2">
-        <v>12.05781538122944</v>
+        <v>12.151257625073</v>
       </c>
       <c r="G2">
-        <v>0.329897837489999</v>
+        <v>0.2556338343837579</v>
       </c>
       <c r="H2">
-        <v>1.503237180419744E-19</v>
+        <v>8.489602920562435E-19</v>
       </c>
       <c r="I2">
-        <v>5.091752598472987E+51</v>
+        <v>8.813160280864544E+61</v>
       </c>
       <c r="J2">
-        <v>1.503237180419744E-19</v>
+        <v>8.489602920562435E-19</v>
       </c>
       <c r="K2">
-        <v>5.091752598472987E+51</v>
+        <v>8.813160280864544E+61</v>
       </c>
     </row>
     <row r="3">
@@ -466,31 +466,31 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.8417413994285633</v>
+        <v>0.7783648129384468</v>
       </c>
       <c r="D3">
-        <v>0.2443431276808681</v>
+        <v>0.2739385779412261</v>
       </c>
       <c r="E3">
-        <v>-0.7050840353785236</v>
+        <v>-0.9146574219644331</v>
       </c>
       <c r="F3">
-        <v>12.61631691212207</v>
+        <v>12.47005131653511</v>
       </c>
       <c r="G3">
-        <v>0.4935703267029977</v>
+        <v>0.3777186095440324</v>
       </c>
       <c r="H3">
-        <v>0.4956971087607971</v>
+        <v>0.4295852412802238</v>
       </c>
       <c r="I3">
-        <v>1.429357910283602</v>
+        <v>1.410317962077051</v>
       </c>
       <c r="J3">
-        <v>0.4956971087607971</v>
+        <v>0.4295852412802238</v>
       </c>
       <c r="K3">
-        <v>1.429357910283602</v>
+        <v>1.410317962077051</v>
       </c>
     </row>
     <row r="4">
@@ -505,31 +505,31 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.090763983792197</v>
+        <v>1.102767007785258</v>
       </c>
       <c r="D4">
-        <v>0.08518230152161964</v>
+        <v>0.09154924065839036</v>
       </c>
       <c r="E4">
-        <v>1.01991084689308</v>
+        <v>1.068523149354061</v>
       </c>
       <c r="F4">
-        <v>17.40266178454178</v>
+        <v>17.03134890276631</v>
       </c>
       <c r="G4">
-        <v>0.3217409406154322</v>
+        <v>0.3001962442856553</v>
       </c>
       <c r="H4">
-        <v>0.9116270132744394</v>
+        <v>0.9090979344094483</v>
       </c>
       <c r="I4">
-        <v>1.305101813585743</v>
+        <v>1.337694243304632</v>
       </c>
       <c r="J4">
-        <v>0.9116270132744394</v>
+        <v>0.9090979344094483</v>
       </c>
       <c r="K4">
-        <v>1.305101813585743</v>
+        <v>1.337694243304632</v>
       </c>
     </row>
     <row r="5">
@@ -544,31 +544,31 @@
         </is>
       </c>
       <c r="C5">
-        <v>1.014838408243666</v>
+        <v>1.019744791060411</v>
       </c>
       <c r="D5">
-        <v>0.03133957244547255</v>
+        <v>0.03256925499476392</v>
       </c>
       <c r="E5">
-        <v>0.4699935247777364</v>
+        <v>0.6003327724301749</v>
       </c>
       <c r="F5">
-        <v>16.90279194659974</v>
+        <v>16.72812323578668</v>
       </c>
       <c r="G5">
-        <v>0.6443664317561473</v>
+        <v>0.5563309537591975</v>
       </c>
       <c r="H5">
-        <v>0.9498793516533961</v>
+        <v>0.9519451104859391</v>
       </c>
       <c r="I5">
-        <v>1.084239796405575</v>
+        <v>1.092373317999412</v>
       </c>
       <c r="J5">
-        <v>0.9498793516533961</v>
+        <v>0.9519451104859391</v>
       </c>
       <c r="K5">
-        <v>1.084239796405575</v>
+        <v>1.092373317999412</v>
       </c>
     </row>
     <row r="6">
@@ -583,31 +583,31 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.9800038798772472</v>
+        <v>0.9655733923796889</v>
       </c>
       <c r="D6">
-        <v>0.04443050764636024</v>
+        <v>0.04971219175700235</v>
       </c>
       <c r="E6">
-        <v>-0.4546143930587224</v>
+        <v>-0.7047197854458657</v>
       </c>
       <c r="F6">
-        <v>13.7485460016857</v>
+        <v>13.2760255117854</v>
       </c>
       <c r="G6">
-        <v>0.6564817740457372</v>
+        <v>0.493163042298204</v>
       </c>
       <c r="H6">
-        <v>0.8907811719861729</v>
+        <v>0.8674449004653398</v>
       </c>
       <c r="I6">
-        <v>1.078163341096489</v>
+        <v>1.074802532785047</v>
       </c>
       <c r="J6">
-        <v>0.8907811719861729</v>
+        <v>0.8674449004653398</v>
       </c>
       <c r="K6">
-        <v>1.078163341096489</v>
+        <v>1.074802532785047</v>
       </c>
     </row>
     <row r="7">
@@ -622,31 +622,31 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.5206710506349949</v>
+        <v>0.4561198079941201</v>
       </c>
       <c r="D7">
-        <v>0.5761010443044489</v>
+        <v>0.6338966010187216</v>
       </c>
       <c r="E7">
-        <v>-1.132851300695794</v>
+        <v>-1.23837194565527</v>
       </c>
       <c r="F7">
-        <v>13.46970183068307</v>
+        <v>13.46800170162188</v>
       </c>
       <c r="G7">
-        <v>0.2770396197174178</v>
+        <v>0.2367298199615641</v>
       </c>
       <c r="H7">
-        <v>0.1506448704816027</v>
+        <v>0.1165274492978086</v>
       </c>
       <c r="I7">
-        <v>1.799585622150054</v>
+        <v>1.785375724760719</v>
       </c>
       <c r="J7">
-        <v>0.1506448704816027</v>
+        <v>0.1165274492978086</v>
       </c>
       <c r="K7">
-        <v>1.799585622150054</v>
+        <v>1.785375724760719</v>
       </c>
     </row>
     <row r="8">
@@ -661,31 +661,31 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.993972932592975</v>
+        <v>1.00040760418943</v>
       </c>
       <c r="D8">
-        <v>0.2320350667526815</v>
+        <v>0.2341726515342241</v>
       </c>
       <c r="E8">
-        <v>-0.02605340465433581</v>
+        <v>0.001740259328914386</v>
       </c>
       <c r="F8">
-        <v>17.90855542893837</v>
+        <v>17.88665525048673</v>
       </c>
       <c r="G8">
-        <v>0.9795028657589765</v>
+        <v>0.9986307370398664</v>
       </c>
       <c r="H8">
-        <v>0.610356921537614</v>
+        <v>0.6115280061201829</v>
       </c>
       <c r="I8">
-        <v>1.618695808738515</v>
+        <v>1.636581423097321</v>
       </c>
       <c r="J8">
-        <v>0.610356921537614</v>
+        <v>0.6115280061201829</v>
       </c>
       <c r="K8">
-        <v>1.618695808738515</v>
+        <v>1.636581423097321</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +695,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -767,31 +767,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2959140161837668</v>
+        <v>0.03379811872884152</v>
       </c>
       <c r="D2">
-        <v>3.18376968199996</v>
+        <v>1.453604923895495</v>
       </c>
       <c r="E2">
-        <v>-0.3824668472745812</v>
+        <v>-2.330310032160927</v>
       </c>
       <c r="F2">
-        <v>18.24683942690312</v>
+        <v>19.78864377032099</v>
       </c>
       <c r="G2">
-        <v>0.7065335780805783</v>
+        <v>0.03049271331639071</v>
       </c>
       <c r="H2">
-        <v>0.0003707219658244163</v>
+        <v>0.001626061625771719</v>
       </c>
       <c r="I2">
-        <v>236.2015554683365</v>
+        <v>0.7025027904872504</v>
       </c>
       <c r="J2">
-        <v>0.0003707219658244163</v>
+        <v>0.001626061625771719</v>
       </c>
       <c r="K2">
-        <v>236.2015554683365</v>
+        <v>0.7025027904872504</v>
       </c>
     </row>
     <row r="3">
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="C3">
-        <v>1.010963805614005</v>
+        <v>1.009504344025705</v>
       </c>
       <c r="D3">
-        <v>0.00574181905012089</v>
+        <v>0.004942993315624798</v>
       </c>
       <c r="E3">
-        <v>1.899073921117314</v>
+        <v>1.913711248084164</v>
       </c>
       <c r="F3">
-        <v>18.85549633554915</v>
+        <v>19.78899086819717</v>
       </c>
       <c r="G3">
-        <v>0.07296465317951166</v>
+        <v>0.07023342563912509</v>
       </c>
       <c r="H3">
-        <v>0.9988807635451343</v>
+        <v>0.999141874134326</v>
       </c>
       <c r="I3">
-        <v>1.023193011180028</v>
+        <v>1.019974286924701</v>
       </c>
       <c r="J3">
-        <v>0.9988807635451343</v>
+        <v>0.999141874134326</v>
       </c>
       <c r="K3">
-        <v>1.023193011180028</v>
+        <v>1.019974286924701</v>
       </c>
     </row>
     <row r="4">
@@ -845,31 +845,31 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.890643562793229</v>
+        <v>1.658298601008198</v>
       </c>
       <c r="D4">
-        <v>0.5519410170687293</v>
+        <v>0.4435584031008883</v>
       </c>
       <c r="E4">
-        <v>1.153958957260234</v>
+        <v>1.140305614934799</v>
       </c>
       <c r="F4">
-        <v>16.30604571315704</v>
+        <v>18.45499287908831</v>
       </c>
       <c r="G4">
-        <v>0.2651506825045422</v>
+        <v>0.2687422111858491</v>
       </c>
       <c r="H4">
-        <v>0.5878031691732049</v>
+        <v>0.6541324716742544</v>
       </c>
       <c r="I4">
-        <v>6.081173544129336</v>
+        <v>4.2039714724255</v>
       </c>
       <c r="J4">
-        <v>0.5878031691732049</v>
+        <v>0.6541324716742544</v>
       </c>
       <c r="K4">
-        <v>6.081173544129336</v>
+        <v>4.2039714724255</v>
       </c>
     </row>
     <row r="5">
@@ -880,35 +880,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Procalcitonin</t>
         </is>
       </c>
       <c r="C5">
-        <v>0.9742385025828484</v>
+        <v>1.061760449519656</v>
       </c>
       <c r="D5">
-        <v>0.03572045745961159</v>
+        <v>0.25779072927046</v>
       </c>
       <c r="E5">
-        <v>-0.730649549018439</v>
+        <v>0.2324689181864016</v>
       </c>
       <c r="F5">
-        <v>18.24292027636975</v>
+        <v>16.20549194554785</v>
       </c>
       <c r="G5">
-        <v>0.474273242787674</v>
+        <v>0.8190842864743527</v>
       </c>
       <c r="H5">
-        <v>0.9038666259303371</v>
+        <v>0.6150812267939342</v>
       </c>
       <c r="I5">
-        <v>1.050089286058033</v>
+        <v>1.832823378532187</v>
       </c>
       <c r="J5">
-        <v>0.9038666259303371</v>
+        <v>0.6150812267939342</v>
       </c>
       <c r="K5">
-        <v>1.050089286058033</v>
+        <v>1.832823378532187</v>
       </c>
     </row>
     <row r="6">
@@ -919,74 +919,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Procalcitonin</t>
+          <t>MRproADM</t>
         </is>
       </c>
       <c r="C6">
-        <v>1.329874988772991</v>
+        <v>1.021184176793561</v>
       </c>
       <c r="D6">
-        <v>0.5031116799531242</v>
+        <v>0.8107415665525139</v>
       </c>
       <c r="E6">
-        <v>0.5666434626180844</v>
+        <v>0.02585646574885507</v>
       </c>
       <c r="F6">
-        <v>14.80439075742682</v>
+        <v>15.40711018279462</v>
       </c>
       <c r="G6">
-        <v>0.5794465440768753</v>
+        <v>0.979703757855879</v>
       </c>
       <c r="H6">
-        <v>0.4545226133845285</v>
+        <v>0.1821138287068799</v>
       </c>
       <c r="I6">
-        <v>3.891043995797294</v>
+        <v>5.726183070984694</v>
       </c>
       <c r="J6">
-        <v>0.4545226133845285</v>
+        <v>0.1821138287068799</v>
       </c>
       <c r="K6">
-        <v>3.891043995797294</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MRproADM</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.9277731574295517</v>
-      </c>
-      <c r="D7">
-        <v>1.054079579242623</v>
-      </c>
-      <c r="E7">
-        <v>-0.07112178243294848</v>
-      </c>
-      <c r="F7">
-        <v>13.90294727454531</v>
-      </c>
-      <c r="G7">
-        <v>0.944313784018856</v>
-      </c>
-      <c r="H7">
-        <v>0.09659528365541281</v>
-      </c>
-      <c r="I7">
-        <v>8.911025456661267</v>
-      </c>
-      <c r="J7">
-        <v>0.09659528365541281</v>
-      </c>
-      <c r="K7">
-        <v>8.911025456661267</v>
+        <v>5.726183070984694</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +957,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1068,31 +1029,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>243.1003689769828</v>
+        <v>62.8817929399299</v>
       </c>
       <c r="D2">
-        <v>3.535873804507223</v>
+        <v>3.98022953448345</v>
       </c>
       <c r="E2">
-        <v>1.553639836387123</v>
+        <v>1.040456743891687</v>
       </c>
       <c r="F2">
-        <v>22.08241743713067</v>
+        <v>19.8846435399602</v>
       </c>
       <c r="G2">
-        <v>0.1344861479983948</v>
+        <v>0.3106141198803725</v>
       </c>
       <c r="H2">
-        <v>0.1591524752737664</v>
+        <v>0.01553832819064234</v>
       </c>
       <c r="I2">
-        <v>371328.1197486127</v>
+        <v>254475.2456523287</v>
       </c>
       <c r="J2">
-        <v>0.1591524752737664</v>
+        <v>0.01553832819064234</v>
       </c>
       <c r="K2">
-        <v>371328.1197486127</v>
+        <v>254475.2456523287</v>
       </c>
     </row>
     <row r="3">
@@ -1107,31 +1068,31 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.8997003833095336</v>
+        <v>0.8784195155086378</v>
       </c>
       <c r="D3">
-        <v>0.06326582166846589</v>
+        <v>0.08450364203494416</v>
       </c>
       <c r="E3">
-        <v>-1.670625240141957</v>
+        <v>-1.534028454193215</v>
       </c>
       <c r="F3">
-        <v>22.08078046869509</v>
+        <v>18.51885241723475</v>
       </c>
       <c r="G3">
-        <v>0.1089112948347575</v>
+        <v>0.1419299977901614</v>
       </c>
       <c r="H3">
-        <v>0.7890931237115157</v>
+        <v>0.7357898842672469</v>
       </c>
       <c r="I3">
-        <v>1.025811473201042</v>
+        <v>1.048697273128274</v>
       </c>
       <c r="J3">
-        <v>0.7890931237115157</v>
+        <v>0.7357898842672469</v>
       </c>
       <c r="K3">
-        <v>1.025811473201042</v>
+        <v>1.048697273128274</v>
       </c>
     </row>
     <row r="4">
@@ -1146,31 +1107,109 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.6770250712697189</v>
+        <v>6.280084602086688</v>
       </c>
       <c r="D4">
-        <v>6.859403657946469</v>
+        <v>8.260041002974871</v>
       </c>
       <c r="E4">
-        <v>-0.05686310258312202</v>
+        <v>0.2224424129852966</v>
       </c>
       <c r="F4">
-        <v>22.04468903911133</v>
+        <v>19.02564239837758</v>
       </c>
       <c r="G4">
-        <v>0.9551665101718974</v>
+        <v>0.8263400066987004</v>
       </c>
       <c r="H4">
-        <v>4.500497705311259E-07</v>
+        <v>1.951486791614403E-07</v>
       </c>
       <c r="I4">
-        <v>1018471.682780397</v>
+        <v>202099562.1330305</v>
       </c>
       <c r="J4">
-        <v>4.500497705311259E-07</v>
+        <v>1.951486791614403E-07</v>
       </c>
       <c r="K4">
-        <v>1018471.682780397</v>
+        <v>202099562.1330305</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rate_of_reoxygenation</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0.7440330512649164</v>
+      </c>
+      <c r="D5">
+        <v>0.759684927540508</v>
+      </c>
+      <c r="E5">
+        <v>-0.3892005891834909</v>
+      </c>
+      <c r="F5">
+        <v>18.86055913992774</v>
+      </c>
+      <c r="G5">
+        <v>0.7014871658721759</v>
+      </c>
+      <c r="H5">
+        <v>0.151600778300663</v>
+      </c>
+      <c r="I5">
+        <v>3.651598544413019</v>
+      </c>
+      <c r="J5">
+        <v>0.151600778300663</v>
+      </c>
+      <c r="K5">
+        <v>3.651598544413019</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>peak_StO2_post_vascular_occlusion</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>1.049651244528443</v>
+      </c>
+      <c r="D6">
+        <v>0.08434779467506162</v>
+      </c>
+      <c r="E6">
+        <v>0.5745018125793663</v>
+      </c>
+      <c r="F6">
+        <v>17.45029616317056</v>
+      </c>
+      <c r="G6">
+        <v>0.5729606849809417</v>
+      </c>
+      <c r="H6">
+        <v>0.8788411084670281</v>
+      </c>
+      <c r="I6">
+        <v>1.253659762299847</v>
+      </c>
+      <c r="J6">
+        <v>0.8788411084670281</v>
+      </c>
+      <c r="K6">
+        <v>1.253659762299847</v>
       </c>
     </row>
   </sheetData>
@@ -1252,31 +1291,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.374051551800795</v>
+        <v>1.389981485575251</v>
       </c>
       <c r="D2">
-        <v>2.538991623722392</v>
+        <v>2.595538587094385</v>
       </c>
       <c r="E2">
-        <v>0.125153509618957</v>
+        <v>0.1268678604745714</v>
       </c>
       <c r="F2">
-        <v>19.29490908543382</v>
+        <v>16.01390659313327</v>
       </c>
       <c r="G2">
-        <v>0.9016968058925793</v>
+        <v>0.9006243211647613</v>
       </c>
       <c r="H2">
-        <v>0.006799441869753869</v>
+        <v>0.005669710258290104</v>
       </c>
       <c r="I2">
-        <v>277.6724477055521</v>
+        <v>340.7667133284262</v>
       </c>
       <c r="J2">
-        <v>0.006799441869753869</v>
+        <v>0.005669710258290104</v>
       </c>
       <c r="K2">
-        <v>277.6724477055521</v>
+        <v>340.7667133284262</v>
       </c>
     </row>
     <row r="3">
@@ -1291,31 +1330,31 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.6634144664946261</v>
+        <v>0.6429693114731063</v>
       </c>
       <c r="D3">
-        <v>1.016767105028232</v>
+        <v>1.071441900095487</v>
       </c>
       <c r="E3">
-        <v>-0.4035883380602682</v>
+        <v>-0.4122092695335229</v>
       </c>
       <c r="F3">
-        <v>19.09803870694624</v>
+        <v>15.71801575382534</v>
       </c>
       <c r="G3">
-        <v>0.6909985211398476</v>
+        <v>0.6857531762381499</v>
       </c>
       <c r="H3">
-        <v>0.07904529863738527</v>
+        <v>0.06611696591619833</v>
       </c>
       <c r="I3">
-        <v>5.567930818673519</v>
+        <v>6.252699738523803</v>
       </c>
       <c r="J3">
-        <v>0.07904529863738527</v>
+        <v>0.06611696591619833</v>
       </c>
       <c r="K3">
-        <v>5.567930818673519</v>
+        <v>6.252699738523803</v>
       </c>
     </row>
   </sheetData>
@@ -1325,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1396,38 +1435,20 @@
           <t>(Intercept)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="C2">
+        <v>1.237983598876093E+184</v>
       </c>
       <c r="D2">
-        <v>43203305.19980987</v>
+        <v>42388970.33200665</v>
       </c>
       <c r="E2">
-        <v>9.811123480322153E-05</v>
+        <v>9.999986735156252E-06</v>
       </c>
       <c r="F2">
-        <v>11.3749999924712</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.9999234181149923</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.999999683991645</v>
       </c>
     </row>
     <row r="3">
@@ -1442,35 +1463,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>9.910565675314065E-10</v>
+        <v>2.563687264633408E-05</v>
       </c>
       <c r="D3">
-        <v>292978.4382510229</v>
+        <v>970005.0662278049</v>
       </c>
       <c r="E3">
-        <v>-7.076373819769476E-05</v>
+        <v>-1.089837493955943E-05</v>
       </c>
       <c r="F3">
-        <v>11.37499999355787</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0.9999447645269495</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999996556017905</v>
       </c>
     </row>
     <row r="4">
@@ -1485,35 +1490,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>90.62802295849582</v>
+        <v>1.060094103732531</v>
       </c>
       <c r="D4">
-        <v>65826.84644031776</v>
+        <v>95821.34172751073</v>
       </c>
       <c r="E4">
-        <v>6.846391272120252E-05</v>
+        <v>6.090259250975215E-07</v>
       </c>
       <c r="F4">
-        <v>11.37499998435898</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.9999465596829321</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999999807542461</v>
       </c>
     </row>
     <row r="5">
@@ -1528,35 +1517,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>2.46856248547242</v>
+        <v>68.6278161783048</v>
       </c>
       <c r="D5">
-        <v>58537.91937277903</v>
+        <v>162141.5511669441</v>
       </c>
       <c r="E5">
-        <v>1.543676306252652E-05</v>
+        <v>2.608028544046904E-05</v>
       </c>
       <c r="F5">
-        <v>11.37499999715825</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>0.9999879506519499</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999991758401765</v>
       </c>
     </row>
     <row r="6">
@@ -1571,35 +1544,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.09814089713666606</v>
+        <v>12.28266094938987</v>
       </c>
       <c r="D6">
-        <v>36023.91604206437</v>
+        <v>151908.5885128964</v>
       </c>
       <c r="E6">
-        <v>-6.443916603222513E-05</v>
+        <v>1.651117039193588E-05</v>
       </c>
       <c r="F6">
-        <v>11.3749999820989</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0.9999497012465721</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999994782325434</v>
       </c>
     </row>
     <row r="7">
@@ -1614,35 +1571,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>2.703193800284142E-26</v>
+        <v>8.942250451685304E+19</v>
       </c>
       <c r="D7">
-        <v>434532.0678026613</v>
+        <v>3002066.468869584</v>
       </c>
       <c r="E7">
-        <v>-0.0001354854631387971</v>
+        <v>1.530276045822161E-05</v>
       </c>
       <c r="F7">
-        <v>11.37499998861513</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0.9998942452190861</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999995164193535</v>
       </c>
     </row>
     <row r="8">
@@ -1657,35 +1598,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>14.9384096537038</v>
+        <v>4.112903767647621E-10</v>
       </c>
       <c r="D8">
-        <v>994897.4119768033</v>
+        <v>986216.5771982863</v>
       </c>
       <c r="E8">
-        <v>2.71780355703618E-06</v>
+        <v>-2.191376837274573E-05</v>
       </c>
       <c r="F8">
-        <v>11.37499999948328</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>0.9999978785862775</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999993075057358</v>
       </c>
     </row>
     <row r="9">
@@ -1700,35 +1625,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>1.576034900581856</v>
+        <v>0.8126309133303963</v>
       </c>
       <c r="D9">
-        <v>3204.975055794755</v>
+        <v>19002.9388791298</v>
       </c>
       <c r="E9">
-        <v>0.0001419393687346286</v>
+        <v>-1.091821928061107E-05</v>
       </c>
       <c r="F9">
-        <v>11.37499997351423</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0.999889207546769</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.999999654974692</v>
       </c>
     </row>
     <row r="10">
@@ -1743,35 +1652,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>264285.0953837544</v>
+        <v>2.553647554352594E-26</v>
       </c>
       <c r="D10">
-        <v>370555.070272584</v>
+        <v>2738301.986368035</v>
       </c>
       <c r="E10">
-        <v>3.369211409527152E-05</v>
+        <v>-2.152052255764231E-05</v>
       </c>
       <c r="F10">
-        <v>11.37499997834816</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0.9999737012217165</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999993199326459</v>
       </c>
     </row>
     <row r="11">
@@ -1786,35 +1679,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.1339224202347137</v>
+        <v>19219.73963742527</v>
       </c>
       <c r="D11">
-        <v>357549.4407964558</v>
+        <v>905548.4504251847</v>
       </c>
       <c r="E11">
-        <v>-5.622983483580144E-06</v>
+        <v>1.089250733228168E-05</v>
       </c>
       <c r="F11">
-        <v>11.37499999384892</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>0.9999956109137129</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999996557872122</v>
       </c>
     </row>
     <row r="12">
@@ -1829,35 +1706,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.0001890633151890571</v>
+        <v>1.721647813409436E+37</v>
       </c>
       <c r="D12">
-        <v>1185645.424329762</v>
+        <v>4211472.114950551</v>
       </c>
       <c r="E12">
-        <v>-7.231022379942254E-06</v>
+        <v>2.035842288962773E-05</v>
       </c>
       <c r="F12">
-        <v>11.37499998508321</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>0.9999943557399267</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999993566560077</v>
       </c>
     </row>
     <row r="13">
@@ -1872,35 +1733,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>1.303158506770747</v>
+        <v>1.648907668659202E-07</v>
       </c>
       <c r="D13">
-        <v>74928.83154840568</v>
+        <v>600330.6653361367</v>
       </c>
       <c r="E13">
-        <v>3.53389920585154E-06</v>
+        <v>-2.601563355509548E-05</v>
       </c>
       <c r="F13">
-        <v>11.37499999383108</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0.9999972415731631</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999991778832322</v>
       </c>
     </row>
     <row r="14">
@@ -1915,35 +1760,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>6.909479468512413E+295</v>
+        <v>8.485722390091039E-280</v>
       </c>
       <c r="D14">
-        <v>8785997.429345479</v>
+        <v>27685710.44886267</v>
       </c>
       <c r="E14">
-        <v>7.753194810446923E-05</v>
+        <v>-2.321000366571255E-05</v>
       </c>
       <c r="F14">
-        <v>11.37499999437422</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>0.9999394815206435</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.9999992665435731</v>
       </c>
     </row>
     <row r="15">
@@ -1954,38 +1783,397 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>rate_of_reoxygenation</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>1.429850998329986E-44</v>
+      </c>
+      <c r="D15">
+        <v>4793367.53574085</v>
+      </c>
+      <c r="E15">
+        <v>-2.106163841956751E-05</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0.9999993344337843</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>peak_StO2_post_vascular_occlusion</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.05704453585392297</v>
+      </c>
+      <c r="D16">
+        <v>85594.17419601588</v>
+      </c>
+      <c r="E16">
+        <v>-3.345932141244139E-05</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0.9999989426562654</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Microvascular_flox_index</t>
         </is>
       </c>
-      <c r="C15">
-        <v>6.455617085975471E-27</v>
-      </c>
-      <c r="D15">
-        <v>1579018.407336307</v>
-      </c>
-      <c r="E15">
-        <v>-3.819135141983729E-05</v>
-      </c>
-      <c r="F15">
-        <v>11.37499999309591</v>
-      </c>
-      <c r="G15">
-        <v>0.9999701892887912</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Inf</t>
+      <c r="C17">
+        <v>7.702512376503242E-17</v>
+      </c>
+      <c r="D17">
+        <v>3192343.233081376</v>
+      </c>
+      <c r="E17">
+        <v>-1.162230916717006E-05</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0.9999996327248348</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Patient_SexMale</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>2.409757103076759E-35</v>
+      </c>
+      <c r="D18">
+        <v>6128937.124054611</v>
+      </c>
+      <c r="E18">
+        <v>-1.300567303694911E-05</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0.9999995890093254</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BMI</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>170.1073340325425</v>
+      </c>
+      <c r="D19">
+        <v>139873.7836343016</v>
+      </c>
+      <c r="E19">
+        <v>3.672188941358036E-05</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0.9999988395563159</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Frailty_Score</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>3.945502165539304E-51</v>
+      </c>
+      <c r="D20">
+        <v>4573067.327080017</v>
+      </c>
+      <c r="E20">
+        <v>-2.537886613162118E-05</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0.9999991980056352</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hypertension</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>7.946120770218121E-09</v>
+      </c>
+      <c r="D21">
+        <v>1572080.068277178</v>
+      </c>
+      <c r="E21">
+        <v>-1.186363363873622E-05</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0.9999996250987702</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>3.958139688747327E+48</v>
+      </c>
+      <c r="D22">
+        <v>6872295.217266547</v>
+      </c>
+      <c r="E22">
+        <v>1.628274907659464E-05</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0.9999994854508566</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Chronic_Kidney_Disease</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>3.475917817155541E+101</v>
+      </c>
+      <c r="D23">
+        <v>9140393.366293585</v>
+      </c>
+      <c r="E23">
+        <v>2.557952853744575E-05</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0.999999191664529</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Chronic_Respiratory_Disease</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>190.0994415768471</v>
+      </c>
+      <c r="D24">
+        <v>4402378.454583582</v>
+      </c>
+      <c r="E24">
+        <v>1.191980054895864E-06</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0.9999999623323839</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cardiovascular_Disease</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>8.820680650554452E-85</v>
+      </c>
+      <c r="D25">
+        <v>11292328.37911273</v>
+      </c>
+      <c r="E25">
+        <v>-1.713930266358365E-05</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0.999999458383015</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Peripheral_Vascular_Disease</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>1.688605796730857E+144</v>
+      </c>
+      <c r="D26">
+        <v>12192483.23640107</v>
+      </c>
+      <c r="E26">
+        <v>2.723777840561368E-05</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0.9999991392623957</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cancer_Diagnosis</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>1.391448393136073E-53</v>
+      </c>
+      <c r="D27">
+        <v>11280690.02742141</v>
+      </c>
+      <c r="E27">
+        <v>-1.078893794783462E-05</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0.9999996590600955</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chronic_Liver_Disease</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>0.01792950866151961</v>
+      </c>
+      <c r="D28">
+        <v>3611126.256502924</v>
+      </c>
+      <c r="E28">
+        <v>-1.113588146537119E-06</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0.9999999648096369</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Chronic_Neurological_Disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Immunosuppression</t>
         </is>
       </c>
     </row>
